--- a/ViewerSample/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/ViewerSample/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\ViewerSample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7C988D-38C0-4807-BCFB-04E79DC5E258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CC69B6-14DF-4A5E-8DA6-CB5D7387BF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="3555" windowWidth="50490" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1545" yWindow="3675" windowWidth="50490" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -3825,7 +3825,7 @@
       <c r="O22" s="78"/>
       <c r="P22" s="78"/>
       <c r="Q22" s="96">
-        <v>45946</v>
+        <v>45945</v>
       </c>
       <c r="R22" s="21"/>
       <c r="S22" s="18"/>
